--- a/SuperCom.Test/测试用例/测试用例.xlsx
+++ b/SuperCom.Test/测试用例/测试用例.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9420"/>
+    <workbookView windowWidth="20751" windowHeight="10611"/>
   </bookViews>
   <sheets>
-    <sheet name="用户测试用例" sheetId="4" r:id="rId1"/>
+    <sheet name="4.6" sheetId="6" r:id="rId1"/>
+    <sheet name="4.2" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="62">
   <si>
     <t>用例编号</t>
   </si>
@@ -38,6 +52,9 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>自动化</t>
   </si>
   <si>
     <t>应用更新</t>
@@ -132,23 +149,16 @@
     <t>1.所有功能正常</t>
   </si>
   <si>
-    <t>测试设置</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>1.打开设置
-2.测试所有配置（除了语法高亮）</t>
-  </si>
-  <si>
-    <t>1.所有设置项正常</t>
-  </si>
-  <si>
     <t>语法高亮</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1.打开 2 个配对串口
 2.编辑命令新增  5 个，命令分别是：
 </t>
@@ -254,6 +264,62 @@
 3.切换高亮规则也正常</t>
   </si>
   <si>
+    <t>测试 16进制的收发</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1.点击编辑命令，新增【HEX】
+2.添加命令 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="0" tint="-0.5"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">010101010101
+0202020202020202
+030303030303030303030303
+68656c6c6f20776f726c64
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3.修改发送端为 HEX 发送模式，接收端为 HEX 接收模式
+4.切换到 STR 发送模式
+5.接收端切换到 HEX 模式
+6.来回测试 3,4,5,6 步骤</t>
+    </r>
+  </si>
+  <si>
+    <t>1.HEX 收发正常</t>
+  </si>
+  <si>
+    <t>测试设置</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>1.打开设置
+2.测试所有配置（除了语法高亮）</t>
+  </si>
+  <si>
+    <t>1.所有设置项正常</t>
+  </si>
+  <si>
     <t>快捷键</t>
   </si>
   <si>
@@ -276,26 +342,96 @@
 2.关闭所有串口
 3.固定 3 个串口
 4.测试 tab 的右键菜单
-5.重启后菜单正常</t>
+5.重启后菜单正常
+6.测试连接/断开所有</t>
   </si>
   <si>
     <t>虚拟串口模拟</t>
   </si>
   <si>
     <t>1.打开虚拟串口模拟</t>
+  </si>
+  <si>
+    <t>关闭再次启动应用</t>
+  </si>
+  <si>
+    <t>1.打开 SuperCom.exe</t>
+  </si>
+  <si>
+    <t>1.可以正常启动</t>
+  </si>
+  <si>
+    <t>系统休眠</t>
+  </si>
+  <si>
+    <t>1.打开系统设置，查找电源和睡眠，修改屏幕和睡眠在  1 min 后关闭
+2.等待系统休眠，休眠后唤醒系统
+3.打开 SuperCom，设置-勾选防止系统休眠</t>
+  </si>
+  <si>
+    <t>1.防止系统休眠可以正常运行</t>
+  </si>
+  <si>
+    <t>配置导入导出功能</t>
+  </si>
+  <si>
+    <t>1.导入配置
+2.导出配置</t>
+  </si>
+  <si>
+    <t>1.正常运行</t>
+  </si>
+  <si>
+    <t>串口详情</t>
+  </si>
+  <si>
+    <t>1、鼠标悬停在串口上显示串口详细信息
+2、设置里支持隐藏串口类型</t>
+  </si>
+  <si>
+    <t>鼠标滚动决策固定</t>
+  </si>
+  <si>
+    <t>1、连接串口，收集超过一屏的日志
+2、鼠标滚轮向上滚动
+3、鼠标滚轮向下滚动
+4、点击右侧滚动到底部按钮
+5、设置里取消鼠标滚动决策固定，重复步骤 1-4</t>
+  </si>
+  <si>
+    <t>1、上滚时日志固定
+2、2 种方式滚到底部，日志取消固定
+3、取消鼠标滚动决策固定，上述不起作用</t>
+  </si>
+  <si>
+    <t>文件名日期命名补全</t>
+  </si>
+  <si>
+    <t>1、观察文件名是中的日期是否填充 0
+2、设置支持填充 0 和不填充 0</t>
+  </si>
+  <si>
+    <t>自动校验</t>
+  </si>
+  <si>
+    <t>命令发送</t>
+  </si>
+  <si>
+    <t>1、修改自动校验的启用、校验方式、添加位置
+2、命令自动执行是否应用校验</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,34 +451,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -361,6 +469,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -370,41 +517,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -455,24 +570,50 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="0" tint="-0.5"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="0" tint="-0.5"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="0" tint="-0.5"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0" tint="-0.5"/>
       <name val="微软雅黑"/>
@@ -494,49 +635,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,121 +773,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -699,21 +840,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -747,6 +873,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -805,148 +946,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -975,56 +1116,56 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1045,6 +1186,13 @@
           <color rgb="FF00B0F0"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1343,21 +1491,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="40" customHeight="1" outlineLevelCol="7"/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="40" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.1574074074074" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1203703703704" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5555555555556" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1574074074074" style="1" customWidth="1"/>
-    <col min="5" max="5" width="55.8888888888889" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.5555555555556" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.1574074074074" style="1" customWidth="1"/>
-    <col min="8" max="8" width="35.8888888888889" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="13.1531531531532" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1171171171171" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5585585585586" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1531531531532" style="1" customWidth="1"/>
+    <col min="5" max="5" width="55.8918918918919" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.5585585585586" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.1531531531532" style="1" customWidth="1"/>
+    <col min="8" max="8" width="35.8918918918919" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.5585585585586" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:8">
+    <row r="1" customHeight="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1382,8 +1531,11 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="70" customHeight="1" spans="1:7">
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1391,22 +1543,22 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" ht="155" customHeight="1" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="155" customHeight="1" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1414,22 +1566,22 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" ht="73" customHeight="1" spans="1:6">
+    </row>
+    <row r="4" ht="73" customHeight="1" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1437,19 +1589,22 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="111" customHeight="1" spans="1:7">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="111" customHeight="1" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1457,22 +1612,22 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="94" customHeight="1" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" ht="217" customHeight="1" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1480,7 +1635,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>24</v>
@@ -1488,14 +1643,11 @@
       <c r="E6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="217" customHeight="1" spans="1:7">
+    </row>
+    <row r="7" ht="156" customHeight="1" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1506,7 +1658,7 @@
         <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>28</v>
@@ -1514,34 +1666,28 @@
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="99" customHeight="1" spans="1:7">
+    </row>
+    <row r="8" ht="94" customHeight="1" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="E8" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" ht="51" customHeight="1" spans="1:7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" ht="99" customHeight="1" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1549,82 +1695,714 @@
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="82" customHeight="1" spans="1:7">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="4" t="s">
         <v>36</v>
       </c>
+      <c r="E10" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1" spans="1:7">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="99" customHeight="1" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1" spans="1:9">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1" spans="1:9">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
+      <c r="B13" s="1">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1" spans="1:9">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" ht="47" customHeight="1" spans="1:9">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" ht="95" customHeight="1" spans="1:6">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1" spans="1:6">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1" spans="1:6">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="G7">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G$1:G$1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G6 G8:G12 G14:G1048576">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7 G8 G11 G2:G4 G5:G6 G9:G10 G12:G1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
+      <formula1>"5,4,3,2,1,0"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+      <formula1>"基本功能,命令发送,语法高亮,插件,更新,快捷键,设置,其它"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>"PASS,FAIL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11 D2:D10 D12:D1048576">
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="40" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="13.1531531531532" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1171171171171" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5585585585586" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1531531531532" style="1" customWidth="1"/>
+    <col min="5" max="5" width="55.8918918918919" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.5585585585586" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.1531531531532" style="1" customWidth="1"/>
+    <col min="8" max="8" width="35.8918918918919" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.5585585585586" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:9">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1" spans="1:9">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="155" customHeight="1" spans="1:9">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="73" customHeight="1" spans="1:9">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="111" customHeight="1" spans="1:9">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="217" customHeight="1" spans="1:9">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="156" customHeight="1" spans="1:9">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="94" customHeight="1" spans="1:9">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" ht="99" customHeight="1" spans="1:9">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1" spans="1:9">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="99" customHeight="1" spans="1:9">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1" spans="1:9">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1" spans="1:9">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1" spans="1:9">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" ht="47" customHeight="1" spans="1:9">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" ht="95" customHeight="1" spans="1:7">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1" spans="1:7">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1" spans="1:7">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G$1:G$1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G6 G8:G12 G14:G1048576">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
+      <formula1>"5,4,3,2,1,0"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"基本功能,命令发送,语法高亮,插件,更新,快捷键,设置,其它"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
-      <formula1>"5,4,3,2,1,0"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+      <formula1>"PASS,FAIL"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
